--- a/Coding_Problems/FINAL450.xlsx
+++ b/Coding_Problems/FINAL450.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30026"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30131"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://koerbergroup-my.sharepoint.com/personal/rupesh_kumar_ext_godrejkoerber_com/Documents/Desktop/CPP_AND_Coding_Problems/Coding_Problems/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\RupKumExt\Desktop\CPP_AND_Coding_Problems\Coding_Problems\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="2" documentId="8_{A296DB3B-D750-F440-AE8C-C019300B98C1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{F3EE9903-AEC3-402F-9DB4-734F58892287}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{86D50C8E-806D-4745-93E6-2526693D41F9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{261C335C-1D91-C143-AEEF-19B82073468C}"/>
   </bookViews>
@@ -7374,7 +7374,7 @@
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <headerFooter>
-    <oddFooter>&amp;R_x000D_&amp;1#&amp;"Aptos"&amp;10&amp;K000000 C2 - For Internal Use</oddFooter>
+    <oddFooter>&amp;R_x000D_&amp;1#&amp;"Aptos"&amp;10&amp;K000000 C3 - Confidential</oddFooter>
   </headerFooter>
 </worksheet>
 </file>